--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -104,12 +103,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,19 +537,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1523100000</v>
+        <v>80000000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0.0007</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.1085</v>
+        <v>0.1321</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -565,13 +564,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>105300000</v>
+        <v>20000000</v>
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="7" t="n">
-        <v>0.065</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -586,7 +585,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>1628400000</v>
+        <v>100000000</v>
       </c>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>

--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -506,17 +506,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>W금융일수</t>
+          <t>가중평균 금융일수</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>S입금부족율</t>
+          <t>입금부족률</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ty수익율</t>
+          <t>예상 연환산수익률</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">

--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>투자자산 현황 — 기준일 2026-08-27 / ㈜테스트인베스트</t>
+          <t>투자자산 현황 — 2026-08-27 / ㈜테스트인베스트</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>예상 연환산수익률</t>
+          <t>예상 연환산 수익률</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">

--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -95,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,10 +103,8 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" min="1" max="1"/>
@@ -482,8 +478,6 @@
     <col width="12.5" customWidth="1" min="3" max="3"/>
     <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="11.5" customWidth="1" min="5" max="5"/>
-    <col width="11.5" customWidth="1" min="6" max="6"/>
-    <col width="13.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -519,16 +513,6 @@
           <t>예상 연환산 수익률</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>비중</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>보관</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -543,18 +527,10 @@
         <v>3.04</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.1321</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>㈜페이허그</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -569,35 +545,23 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>㈜쿠콘</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>합계 (투자자산)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>100000000</v>
       </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
